--- a/output/pdf_financials_xlsx/HRC.P.xlsx
+++ b/output/pdf_financials_xlsx/HRC.P.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.05784</v>
+        <v>-0.05784</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.097819</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.05784</v>
+        <v>-0.05784</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.097819</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.05784</v>
+        <v>-0.05784</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.097819</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-2.892</v>
+        <v>2.892</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>4.89095</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.05784</v>
+        <v>-0.05784</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.097819</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.05784</v>
+        <v>-0.05784</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.097819</v>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.05784</v>
+        <v>-0.05784</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.097819</v>
+        <v>-0.097819</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HRC.P.xlsx
+++ b/output/pdf_financials_xlsx/HRC.P.xlsx
@@ -628,16 +628,16 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.097819</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.018788</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.033592</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="11">
@@ -650,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.097819</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.018788</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.033592</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="12">
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.136657</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.340448</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.321822</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.298826</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.266133</v>
       </c>
     </row>
     <row r="35">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.136657</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.340448</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.321822</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.298826</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.266133</v>
       </c>
     </row>
     <row r="37">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">

--- a/output/pdf_financials_xlsx/HRC.P.xlsx
+++ b/output/pdf_financials_xlsx/HRC.P.xlsx
@@ -3499,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4797,7 +4797,11 @@
           <t>Proceeds from share issuance 6 $</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.18</v>
       </c>
@@ -5036,114 +5040,134 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Financing costs paid 11</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>0.050977</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.01094</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.000763</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0.001905</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0.001766</v>
+        <v>-0.0255</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.006863</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.02436</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.018025</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.031687</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.020234</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Total expenses $</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.097819</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.018788</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0.033592</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>0.022</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.136657</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -5159,32 +5183,28 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss $</t>
+          <t>Professional fees $</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.050977</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.01094</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.018788</v>
+        <v>0.000763</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-0.033592</v>
+        <v>0.001905</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.022</v>
+        <v>0.001766</v>
       </c>
     </row>
     <row r="42">
@@ -5200,32 +5220,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted $</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.006863</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.02436</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0</v>
+        <v>0.018025</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.031687</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0</v>
+        <v>0.020234</v>
       </c>
     </row>
     <row r="43">
@@ -5241,12 +5257,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 6</t>
+          <t>Total expenses $</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5255,16 +5271,16 @@
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>6.279452</v>
+        <v>0.097819</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>6.6</v>
+        <v>0.018788</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>6.6</v>
+        <v>0.033592</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>6.6</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="44">
@@ -5275,15 +5291,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>($)                  ($)             ($)                   ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>As at December 31, 2023 406,229 80,786</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Net Loss and Comprehensive Loss $</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5294,16 +5314,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G44" s="5" t="n">
+        <v>-0.018788</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.312568</v>
+        <v>-0.033592</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.174447</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="45">
@@ -5314,17 +5332,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>($)                  ($)             ($)                   ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - -</t>
+          <t>Net loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5337,16 +5355,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>-0.033592</v>
+        <v>-1e-08</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-0.033592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5357,35 +5373,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>($)                  ($)             ($)                   ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>As at December 31, 2024 406,229 80,786</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding 6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="5" t="n">
+        <v>6.279452</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>6.6</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.278976</v>
+        <v>6.6</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>-0.208039</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="47">
@@ -5401,7 +5417,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>As at December 31, 2025 406,229 80,786</t>
+          <t>As at December 31, 2023 406,229 80,786</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5421,10 +5437,10 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.256976</v>
+        <v>0.312568</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-0.230039</v>
+        <v>-0.174447</v>
       </c>
     </row>
     <row r="48">
@@ -5435,15 +5451,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)                  ($)             ($)                   ($)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net of 3,600,000 shares held in escrow 6</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - -</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -5454,16 +5474,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n">
-        <v>3</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.033592</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>-0.033592</v>
       </c>
     </row>
     <row r="49">
@@ -5474,12 +5494,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>($)                   ($)              ($)                    ($)</t>
+          <t>($)                  ($)             ($)                   ($)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>As at December 31, 2022 406,229 80,786</t>
+          <t>As at December 31, 2024 406,229 80,786</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -5493,16 +5513,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n">
-        <v>0.331356</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>-0.155659</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.278976</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.208039</v>
       </c>
     </row>
     <row r="50">
@@ -5513,19 +5533,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>($)                   ($)              ($)                    ($)</t>
+          <t>($)                  ($)             ($)                   ($)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - -</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>As at December 31, 2025 406,229 80,786</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5536,16 +5552,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.018788</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-0.018788</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.256976</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.230039</v>
       </c>
     </row>
     <row r="51">
@@ -5556,12 +5572,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>($)                   ($)              ($)                    ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>As at December 31, 2023 406,229 80,786</t>
+          <t>Net of 3,600,000 shares held in escrow 6</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5576,10 +5592,10 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.312568</v>
+        <v>3</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>-0.174447</v>
+        <v>3</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5600,7 +5616,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>As at December 31, 2024 406,229 80,786</t>
+          <t>As at December 31, 2022 406,229 80,786</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -5615,10 +5631,10 @@
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.278976</v>
+        <v>0.331356</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-0.208039</v>
+        <v>-0.155659</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5634,32 +5650,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)                   ($)              ($)                    ($)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Share-basesd compensation 6</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - -</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>0.06251900000000001</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.018788</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.018788</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5675,34 +5693,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)                   ($)              ($)                    ($)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Loss and Comprehensive Loss $</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>As at December 31, 2023 406,229 80,786</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>-0.097819</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.018788</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.312568</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>-0.174447</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5718,34 +5732,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>($)                   ($)              ($)                    ($)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Net income (loss) per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>As at December 31, 2024 406,229 80,786</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.278976</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>-0.208039</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5761,23 +5771,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2021 180,000 -</t>
+          <t>Share-basesd compensation 6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>0.12216</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.12216</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.05784</v>
+        <v>0.06251900000000001</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5798,25 +5812,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Issuance of common shares 6 300,000 -</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>0.3</v>
+          <t>Loss and Comprehensive Loss $</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.097819</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.018788</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5837,25 +5855,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Share issuance costs 6 (73,771) 18,267</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>-0.055504</v>
+          <t>Net income (loss) per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.055504</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -5881,20 +5903,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Share based compensations 6 - 62,519</t>
+          <t>Balance at December 31, 2021 180,000 -</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.06251900000000001</v>
+        <v>0.12216</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.06251900000000001</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.12216</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.05784</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -5920,22 +5940,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss - -</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of common shares 6 300,000 -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>-0.05784</v>
+        <v>0.3</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.097819</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.097819</v>
+        <v>0.3</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -5961,18 +5979,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 406,229 80,786</t>
+          <t>Share issuance costs 6 (73,771) 18,267</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>0.331356</v>
+        <v>-0.055504</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.331356</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.155659</v>
+        <v>-0.055504</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -5998,20 +6018,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 406,229 80,786</t>
+          <t>Share based compensations 6 - 62,519</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" s="5" t="n">
+        <v>0.06251900000000001</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.312568</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.174447</v>
+        <v>0.06251900000000001</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -6032,25 +6052,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>For the period from</t>
+          <t>Note             ($)               ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Loss and comprehensive loss - -</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
-        <v>0.002021</v>
+        <v>-0.05784</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.097819</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.097819</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6071,27 +6093,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note             ($)               ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share-based compensation 6</t>
+          <t>Balance at December 31, 2022 406,229 80,786</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>0.331356</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.06251900000000001</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.331356</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.155659</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -6112,29 +6130,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note             ($)               ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>-0.05784</v>
+          <t>Balance at December 31, 2023 406,229 80,786</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>-0.097819</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.312568</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-0.174447</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -6155,24 +6169,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>For the period from</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.002021</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-2e-08</v>
+        <v>1e-06</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -6198,24 +6208,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 6</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>3.008219</v>
+          <t>Share-based compensation 6</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>6.279452</v>
+        <v>0.06251900000000001</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -6241,24 +6249,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>At incorporation, March 1, 2021 - -</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>-0.05784</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>-0.097819</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -6284,22 +6292,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Issuance of common shares 6 180,000 -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -6325,24 +6335,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>At incorporation, March 1, 2021 - - -</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of shares outstanding 6</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>3.008219</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>6.279452</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6373,12 +6383,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Issuance of common shares 6 180,000 - -</t>
+          <t>At incorporation, March 1, 2021 - -</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.18</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6414,12 +6426,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - (57,840)</t>
+          <t>Issuance of common shares 6 180,000 -</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>-0.05784</v>
+        <v>0.18</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6455,29 +6467,154 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>At incorporation, March 1, 2021 - - -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Issuance of common shares 6 180,000 - -</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - (57,840)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>-0.05784</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>Balance at December 31, 2021 180,000 - (57,840)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
         <v>0.12216</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
